--- a/public/templates/Mammography_Template.xlsx
+++ b/public/templates/Mammography_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O51"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -1198,7 +1198,7 @@
         <v>Rec Max</v>
       </c>
       <c r="K21" t="str">
-        <v>Rec kVp</v>
+        <v/>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1242,7 +1242,7 @@
         <v>3.0</v>
       </c>
       <c r="K22" t="str">
-        <v>28</v>
+        <v/>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1286,7 +1286,7 @@
         <v>3.0</v>
       </c>
       <c r="K23" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1344,25 +1344,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>FDD (cm)</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B26" t="str">
-        <v>kV</v>
+        <v>&lt;=</v>
       </c>
       <c r="C26" t="str">
-        <v>mAs</v>
+        <v/>
       </c>
       <c r="D26" t="str">
-        <v>Measured Output 1</v>
+        <v/>
       </c>
       <c r="E26" t="str">
-        <v>Measured Output 2</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v>Measured Output 3</v>
+        <v/>
       </c>
       <c r="G26" t="str">
-        <v>Tolerance</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v/>
@@ -1388,25 +1388,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>65</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B27" t="str">
-        <v>25</v>
+        <v>0.05</v>
       </c>
       <c r="C27" t="str">
-        <v>25</v>
+        <v/>
       </c>
       <c r="D27" t="str">
-        <v>10.5</v>
+        <v/>
       </c>
       <c r="E27" t="str">
-        <v>10.4</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v>10.6</v>
+        <v/>
       </c>
       <c r="G27" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1432,22 +1432,22 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>FDD (cm)</v>
       </c>
       <c r="B28" t="str">
-        <v>28</v>
+        <v>kV</v>
       </c>
       <c r="C28" t="str">
-        <v>25</v>
+        <v>mAs</v>
       </c>
       <c r="D28" t="str">
-        <v>12.1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="E28" t="str">
-        <v>12.0</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="F28" t="str">
-        <v>12.2</v>
+        <v>Measured Output 3</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1476,22 +1476,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>65</v>
       </c>
       <c r="B29" t="str">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C29" t="str">
         <v>25</v>
       </c>
       <c r="D29" t="str">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="E29" t="str">
-        <v>14.4</v>
+        <v>10.4</v>
       </c>
       <c r="F29" t="str">
-        <v>14.6</v>
+        <v>10.6</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1523,19 +1523,19 @@
         <v/>
       </c>
       <c r="B30" t="str">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C30" t="str">
         <v>25</v>
       </c>
       <c r="D30" t="str">
-        <v>16.2</v>
+        <v>12.1</v>
       </c>
       <c r="E30" t="str">
-        <v>16.1</v>
+        <v>12.0</v>
       </c>
       <c r="F30" t="str">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1567,19 +1567,19 @@
         <v/>
       </c>
       <c r="B31" t="str">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C31" t="str">
         <v>25</v>
       </c>
       <c r="D31" t="str">
-        <v>18.0</v>
+        <v>14.5</v>
       </c>
       <c r="E31" t="str">
-        <v>17.9</v>
+        <v>14.4</v>
       </c>
       <c r="F31" t="str">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1603,27 +1603,71 @@
         <v/>
       </c>
       <c r="N31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v/>
+      </c>
+      <c r="B32" t="str">
+        <v>40</v>
+      </c>
+      <c r="C32" t="str">
+        <v>25</v>
+      </c>
+      <c r="D32" t="str">
+        <v>16.2</v>
+      </c>
+      <c r="E32" t="str">
+        <v>16.1</v>
+      </c>
+      <c r="F32" t="str">
+        <v>16.3</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL</v>
+        <v/>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>49</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>18.0</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>17.9</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>18.1</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1648,152 +1692,149 @@
       </c>
       <c r="N33" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>FDD (cm)</v>
-      </c>
-      <c r="B34" t="str">
-        <v>kV</v>
-      </c>
-      <c r="C34" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Time (Sec)</v>
-      </c>
-      <c r="E34" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="F34" t="str">
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <v>Tol Value</v>
-      </c>
-      <c r="H34" t="str">
-        <v>Tol Operator</v>
-      </c>
-      <c r="I34" t="str">
-        <v>Tol Time</v>
-      </c>
-      <c r="J34" t="str">
-        <v>Location</v>
-      </c>
-      <c r="K34" t="str">
-        <v>Left</v>
-      </c>
-      <c r="L34" t="str">
-        <v>Right</v>
-      </c>
-      <c r="M34" t="str">
-        <v>Front</v>
-      </c>
-      <c r="N34" t="str">
-        <v>Back</v>
-      </c>
-      <c r="O34" t="str">
-        <v>Top</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>100</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL</v>
       </c>
       <c r="B35" t="str">
-        <v>120</v>
+        <v/>
       </c>
       <c r="C35" t="str">
-        <v>21</v>
+        <v/>
       </c>
       <c r="D35" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="E35" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="F35" t="str">
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H35" t="str">
-        <v>&lt;=</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="J35" t="str">
-        <v>TUBE</v>
+        <v/>
       </c>
       <c r="K35" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="L35" t="str">
-        <v>0.03</v>
+        <v/>
       </c>
       <c r="M35" t="str">
-        <v>0.06</v>
+        <v/>
       </c>
       <c r="N35" t="str">
-        <v>0.04</v>
-      </c>
-      <c r="O35" t="str">
-        <v>0.02</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>FDD (cm)</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>kV</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>mA</v>
       </c>
       <c r="D36" t="str">
-        <v/>
+        <v>Time (Sec)</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>Workload</v>
       </c>
       <c r="F36" t="str">
         <v/>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>Tol Value</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>Tol Operator</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>Tol Time</v>
       </c>
       <c r="J36" t="str">
-        <v>COLLIMATOR</v>
+        <v>Location</v>
       </c>
       <c r="K36" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Right</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Front</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Back</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Top</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>100</v>
+      </c>
+      <c r="B37" t="str">
+        <v>120</v>
+      </c>
+      <c r="C37" t="str">
+        <v>21</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2</v>
+      </c>
+      <c r="E37" t="str">
+        <v>500</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>1</v>
+      </c>
+      <c r="H37" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="I37" t="str">
+        <v>1</v>
+      </c>
+      <c r="J37" t="str">
+        <v>TUBE</v>
+      </c>
+      <c r="K37" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="L37" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="M37" t="str">
+        <v>0.06</v>
+      </c>
+      <c r="N37" t="str">
+        <v>0.04</v>
+      </c>
+      <c r="O37" t="str">
         <v>0.02</v>
-      </c>
-      <c r="L36" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="M36" t="str">
-        <v>0.03</v>
-      </c>
-      <c r="N36" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="O36" t="str">
-        <v>0.01</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>TEST: IMAGING PHANTOM</v>
+        <v/>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -1820,77 +1861,36 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>COLLIMATOR</v>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="L38" t="str">
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="N38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B39" t="str">
-        <v>Visible Count</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Tol Operator</v>
-      </c>
-      <c r="D39" t="str">
-        <v>Tol Value</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
-      <c r="G39" t="str">
-        <v/>
-      </c>
-      <c r="H39" t="str">
-        <v/>
-      </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
-      <c r="J39" t="str">
-        <v/>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-      <c r="L39" t="str">
-        <v/>
-      </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
-      <c r="N39" t="str">
-        <v/>
+        <v>0.01</v>
+      </c>
+      <c r="O38" t="str">
+        <v>0.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fibers</v>
+        <v>TEST: IMAGING PHANTOM</v>
       </c>
       <c r="B40" t="str">
-        <v>5</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>&gt;=</v>
+        <v/>
       </c>
       <c r="D40" t="str">
-        <v>4</v>
+        <v/>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1925,16 +1925,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Micro Calcification</v>
+        <v>Name</v>
       </c>
       <c r="B41" t="str">
-        <v>6</v>
+        <v>Visible Count</v>
       </c>
       <c r="C41" t="str">
-        <v>&gt;=</v>
+        <v>Tol Operator</v>
       </c>
       <c r="D41" t="str">
-        <v>6</v>
+        <v>Tol Value</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1969,16 +1969,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Masses</v>
+        <v>Fibers</v>
       </c>
       <c r="B42" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="str">
         <v>&gt;=</v>
       </c>
       <c r="D42" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2008,21 +2008,65 @@
         <v/>
       </c>
       <c r="N42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Micro Calcification</v>
+      </c>
+      <c r="B43" t="str">
+        <v>6</v>
+      </c>
+      <c r="C43" t="str">
+        <v>&gt;=</v>
+      </c>
+      <c r="D43" t="str">
+        <v>6</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY</v>
+        <v>Masses</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>&gt;=</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2052,83 +2096,39 @@
         <v/>
       </c>
       <c r="N44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v/>
-      </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
-      <c r="C45" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D45" t="str">
-        <v>kV</v>
-      </c>
-      <c r="E45" t="str">
-        <v>Time</v>
-      </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="H45" t="str">
-        <v>Location</v>
-      </c>
-      <c r="I45" t="str">
-        <v>mR/hr</v>
-      </c>
-      <c r="J45" t="str">
-        <v>Category</v>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>TEST: RADIATION PROTECTION SURVEY</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="D46" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="E46" t="str">
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="F46" t="str">
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>300</v>
+        <v/>
       </c>
       <c r="H46" t="str">
-        <v>Control Console (Operator Position)</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="J46" t="str">
-        <v>worker</v>
+        <v/>
       </c>
       <c r="K46" t="str">
         <v/>
@@ -2151,28 +2151,28 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v/>
+        <v>mA</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>kV</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>Time</v>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Workload</v>
       </c>
       <c r="H47" t="str">
-        <v>Outside Lead Glass</v>
+        <v>Location</v>
       </c>
       <c r="I47" t="str">
-        <v>0.03</v>
+        <v>mR/hr</v>
       </c>
       <c r="J47" t="str">
-        <v>worker</v>
+        <v>Category</v>
       </c>
       <c r="K47" t="str">
         <v/>
@@ -2195,28 +2195,28 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v/>
+        <v>100</v>
       </c>
       <c r="D48" t="str">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>300</v>
       </c>
       <c r="H48" t="str">
-        <v>Outside Patient Entrance Door</v>
+        <v>Control Console (Operator Position)</v>
       </c>
       <c r="I48" t="str">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J48" t="str">
-        <v>public</v>
+        <v>worker</v>
       </c>
       <c r="K48" t="str">
         <v/>
@@ -2254,37 +2254,125 @@
         <v/>
       </c>
       <c r="H49" t="str">
+        <v>Outside Lead Glass</v>
+      </c>
+      <c r="I49" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="J49" t="str">
+        <v>worker</v>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+      <c r="B50" t="str">
+        <v/>
+      </c>
+      <c r="C50" t="str">
+        <v/>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>Outside Patient Entrance Door</v>
+      </c>
+      <c r="I50" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="J50" t="str">
+        <v>public</v>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v/>
+      </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+      <c r="C51" t="str">
+        <v/>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
         <v>Patient Waiting Area</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I51" t="str">
         <v>0.01</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J51" t="str">
         <v>public</v>
       </c>
-      <c r="K49" t="str">
-        <v/>
-      </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-      <c r="N49" t="str">
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O51"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O47"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -2952,7 +3040,7 @@
         <v>Rec Max</v>
       </c>
       <c r="K17" t="str">
-        <v>Rec kVp</v>
+        <v/>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -2996,7 +3084,7 @@
         <v>3.0</v>
       </c>
       <c r="K18" t="str">
-        <v>28</v>
+        <v/>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -3040,7 +3128,7 @@
         <v>3.0</v>
       </c>
       <c r="K19" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -3098,25 +3186,25 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>FDD (cm)</v>
+        <v>Tolerance Operator</v>
       </c>
       <c r="B22" t="str">
-        <v>kV</v>
+        <v>&lt;=</v>
       </c>
       <c r="C22" t="str">
-        <v>mAs</v>
+        <v/>
       </c>
       <c r="D22" t="str">
-        <v>Measured Output 1</v>
+        <v/>
       </c>
       <c r="E22" t="str">
-        <v>Measured Output 2</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>Measured Output 3</v>
+        <v/>
       </c>
       <c r="G22" t="str">
-        <v>Tolerance</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -3142,25 +3230,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>65</v>
+        <v>Tolerance Value (CoV)</v>
       </c>
       <c r="B23" t="str">
-        <v>25</v>
+        <v>0.05</v>
       </c>
       <c r="C23" t="str">
-        <v>25</v>
+        <v/>
       </c>
       <c r="D23" t="str">
-        <v>10.5</v>
+        <v/>
       </c>
       <c r="E23" t="str">
-        <v>10.4</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>10.6</v>
+        <v/>
       </c>
       <c r="G23" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -3186,22 +3274,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>FDD (cm)</v>
       </c>
       <c r="B24" t="str">
-        <v>28</v>
+        <v>kV</v>
       </c>
       <c r="C24" t="str">
-        <v>25</v>
+        <v>mAs</v>
       </c>
       <c r="D24" t="str">
-        <v>12.1</v>
+        <v>Measured Output 1</v>
       </c>
       <c r="E24" t="str">
-        <v>12.0</v>
+        <v>Measured Output 2</v>
       </c>
       <c r="F24" t="str">
-        <v>12.2</v>
+        <v>Measured Output 3</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -3230,22 +3318,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>65</v>
       </c>
       <c r="B25" t="str">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C25" t="str">
         <v>25</v>
       </c>
       <c r="D25" t="str">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="E25" t="str">
-        <v>14.4</v>
+        <v>10.4</v>
       </c>
       <c r="F25" t="str">
-        <v>14.6</v>
+        <v>10.6</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -3277,19 +3365,19 @@
         <v/>
       </c>
       <c r="B26" t="str">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C26" t="str">
         <v>25</v>
       </c>
       <c r="D26" t="str">
-        <v>16.2</v>
+        <v>12.1</v>
       </c>
       <c r="E26" t="str">
-        <v>16.1</v>
+        <v>12.0</v>
       </c>
       <c r="F26" t="str">
-        <v>16.3</v>
+        <v>12.2</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -3321,19 +3409,19 @@
         <v/>
       </c>
       <c r="B27" t="str">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C27" t="str">
         <v>25</v>
       </c>
       <c r="D27" t="str">
-        <v>18.0</v>
+        <v>14.5</v>
       </c>
       <c r="E27" t="str">
-        <v>17.9</v>
+        <v>14.4</v>
       </c>
       <c r="F27" t="str">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -3357,27 +3445,71 @@
         <v/>
       </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v/>
+      </c>
+      <c r="B28" t="str">
+        <v>40</v>
+      </c>
+      <c r="C28" t="str">
+        <v>25</v>
+      </c>
+      <c r="D28" t="str">
+        <v>16.2</v>
+      </c>
+      <c r="E28" t="str">
+        <v>16.1</v>
+      </c>
+      <c r="F28" t="str">
+        <v>16.3</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>TEST: RADIATION LEAKAGE LEVEL</v>
+        <v/>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>49</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>25</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>18.0</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>17.9</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>18.1</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -3402,152 +3534,149 @@
       </c>
       <c r="N29" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>FDD (cm)</v>
-      </c>
-      <c r="B30" t="str">
-        <v>kV</v>
-      </c>
-      <c r="C30" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Time (Sec)</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v>Tol Value</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Tol Operator</v>
-      </c>
-      <c r="I30" t="str">
-        <v>Tol Time</v>
-      </c>
-      <c r="J30" t="str">
-        <v>Location</v>
-      </c>
-      <c r="K30" t="str">
-        <v>Left</v>
-      </c>
-      <c r="L30" t="str">
-        <v>Right</v>
-      </c>
-      <c r="M30" t="str">
-        <v>Front</v>
-      </c>
-      <c r="N30" t="str">
-        <v>Back</v>
-      </c>
-      <c r="O30" t="str">
-        <v>Top</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>100</v>
+        <v>TEST: RADIATION LEAKAGE LEVEL</v>
       </c>
       <c r="B31" t="str">
-        <v>120</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>21</v>
+        <v/>
       </c>
       <c r="D31" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="E31" t="str">
-        <v>500</v>
+        <v/>
       </c>
       <c r="F31" t="str">
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v>&lt;=</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="J31" t="str">
-        <v>TUBE</v>
+        <v/>
       </c>
       <c r="K31" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="L31" t="str">
-        <v>0.03</v>
+        <v/>
       </c>
       <c r="M31" t="str">
-        <v>0.06</v>
+        <v/>
       </c>
       <c r="N31" t="str">
-        <v>0.04</v>
-      </c>
-      <c r="O31" t="str">
-        <v>0.02</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>FDD (cm)</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>kV</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>mA</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>Time (Sec)</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>Workload</v>
       </c>
       <c r="F32" t="str">
         <v/>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>Tol Value</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>Tol Operator</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>Tol Time</v>
       </c>
       <c r="J32" t="str">
-        <v>COLLIMATOR</v>
+        <v>Location</v>
       </c>
       <c r="K32" t="str">
+        <v>Left</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Right</v>
+      </c>
+      <c r="M32" t="str">
+        <v>Front</v>
+      </c>
+      <c r="N32" t="str">
+        <v>Back</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Top</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>100</v>
+      </c>
+      <c r="B33" t="str">
+        <v>120</v>
+      </c>
+      <c r="C33" t="str">
+        <v>21</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2</v>
+      </c>
+      <c r="E33" t="str">
+        <v>500</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>1</v>
+      </c>
+      <c r="H33" t="str">
+        <v>&lt;=</v>
+      </c>
+      <c r="I33" t="str">
+        <v>1</v>
+      </c>
+      <c r="J33" t="str">
+        <v>TUBE</v>
+      </c>
+      <c r="K33" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="L33" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="M33" t="str">
+        <v>0.06</v>
+      </c>
+      <c r="N33" t="str">
+        <v>0.04</v>
+      </c>
+      <c r="O33" t="str">
         <v>0.02</v>
-      </c>
-      <c r="L32" t="str">
-        <v>0.02</v>
-      </c>
-      <c r="M32" t="str">
-        <v>0.03</v>
-      </c>
-      <c r="N32" t="str">
-        <v>0.01</v>
-      </c>
-      <c r="O32" t="str">
-        <v>0.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>TEST: IMAGING PHANTOM</v>
+        <v/>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -3574,77 +3703,36 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>COLLIMATOR</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="L34" t="str">
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>0.03</v>
       </c>
       <c r="N34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Visible Count</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Tol Operator</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Tol Value</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-      <c r="J35" t="str">
-        <v/>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
-      <c r="N35" t="str">
-        <v/>
+        <v>0.01</v>
+      </c>
+      <c r="O34" t="str">
+        <v>0.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Fibers</v>
+        <v>TEST: IMAGING PHANTOM</v>
       </c>
       <c r="B36" t="str">
-        <v>5</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>&gt;=</v>
+        <v/>
       </c>
       <c r="D36" t="str">
-        <v>4</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -3679,16 +3767,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Micro Calcification</v>
+        <v>Name</v>
       </c>
       <c r="B37" t="str">
-        <v>6</v>
+        <v>Visible Count</v>
       </c>
       <c r="C37" t="str">
-        <v>&gt;=</v>
+        <v>Tol Operator</v>
       </c>
       <c r="D37" t="str">
-        <v>6</v>
+        <v>Tol Value</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -3723,16 +3811,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Masses</v>
+        <v>Fibers</v>
       </c>
       <c r="B38" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="str">
         <v>&gt;=</v>
       </c>
       <c r="D38" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -3762,21 +3850,65 @@
         <v/>
       </c>
       <c r="N38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Micro Calcification</v>
+      </c>
+      <c r="B39" t="str">
+        <v>6</v>
+      </c>
+      <c r="C39" t="str">
+        <v>&gt;=</v>
+      </c>
+      <c r="D39" t="str">
+        <v>6</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>TEST: RADIATION PROTECTION SURVEY</v>
+        <v>Masses</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>&gt;=</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -3806,83 +3938,39 @@
         <v/>
       </c>
       <c r="N40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v/>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v>mA</v>
-      </c>
-      <c r="D41" t="str">
-        <v>kV</v>
-      </c>
-      <c r="E41" t="str">
-        <v>Time</v>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v>Workload</v>
-      </c>
-      <c r="H41" t="str">
-        <v>Location</v>
-      </c>
-      <c r="I41" t="str">
-        <v>mR/hr</v>
-      </c>
-      <c r="J41" t="str">
-        <v>Category</v>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>TEST: RADIATION PROTECTION SURVEY</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>100</v>
+        <v/>
       </c>
       <c r="D42" t="str">
-        <v>80</v>
+        <v/>
       </c>
       <c r="E42" t="str">
-        <v>0.5</v>
+        <v/>
       </c>
       <c r="F42" t="str">
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>300</v>
+        <v/>
       </c>
       <c r="H42" t="str">
-        <v>Control Console (Operator Position)</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v>0.05</v>
+        <v/>
       </c>
       <c r="J42" t="str">
-        <v>worker</v>
+        <v/>
       </c>
       <c r="K42" t="str">
         <v/>
@@ -3905,28 +3993,28 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v/>
+        <v>mA</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>kV</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>Time</v>
       </c>
       <c r="F43" t="str">
         <v/>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Workload</v>
       </c>
       <c r="H43" t="str">
-        <v>Outside Lead Glass</v>
+        <v>Location</v>
       </c>
       <c r="I43" t="str">
-        <v>0.03</v>
+        <v>mR/hr</v>
       </c>
       <c r="J43" t="str">
-        <v>worker</v>
+        <v>Category</v>
       </c>
       <c r="K43" t="str">
         <v/>
@@ -3949,28 +4037,28 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v/>
+        <v>100</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="F44" t="str">
         <v/>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>300</v>
       </c>
       <c r="H44" t="str">
-        <v>Outside Patient Entrance Door</v>
+        <v>Control Console (Operator Position)</v>
       </c>
       <c r="I44" t="str">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J44" t="str">
-        <v>public</v>
+        <v>worker</v>
       </c>
       <c r="K44" t="str">
         <v/>
@@ -4008,30 +4096,118 @@
         <v/>
       </c>
       <c r="H45" t="str">
+        <v>Outside Lead Glass</v>
+      </c>
+      <c r="I45" t="str">
+        <v>0.03</v>
+      </c>
+      <c r="J45" t="str">
+        <v>worker</v>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+      <c r="C46" t="str">
+        <v/>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>Outside Patient Entrance Door</v>
+      </c>
+      <c r="I46" t="str">
+        <v>0.02</v>
+      </c>
+      <c r="J46" t="str">
+        <v>public</v>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v/>
+      </c>
+      <c r="B47" t="str">
+        <v/>
+      </c>
+      <c r="C47" t="str">
+        <v/>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
         <v>Patient Waiting Area</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I47" t="str">
         <v>0.01</v>
       </c>
-      <c r="J45" t="str">
+      <c r="J47" t="str">
         <v>public</v>
       </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O47"/>
   </ignoredErrors>
 </worksheet>
 </file>